--- a/data/reports/2024-09-02/2024-09-02_duplicates.xlsx
+++ b/data/reports/2024-09-02/2024-09-02_duplicates.xlsx
@@ -145,7 +145,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=470739ea1bc93c102eb2a82fe54bcba1&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004723</t>
+    <t>RMD0005813</t>
   </si>
   <si>
     <t>CoreTel Communications, Inc.</t>
@@ -161,28 +161,28 @@
     <t>Core Communications, Inc., Ton80 Communications, LLC, CoreTel Alabama, Inc., CoreTel Delaware, Inc., CoreTel Florida, Inc., CoreTel Georgia, Inc., CoreTel Kansas, Inc., CoreTel Kentucky, Inc., CoreTel Massachusetts, Inc., CoreTel New Jersey, Inc., CoreTel Virginia, Inc., CoreTel West Virginia, Inc., CoreTel Washington, Inc.,</t>
   </si>
   <si>
+    <t>Glenn Dalgliesh</t>
+  </si>
+  <si>
+    <t>VP of Operations</t>
+  </si>
+  <si>
+    <t>NOC</t>
+  </si>
+  <si>
+    <t>'+14439121000</t>
+  </si>
+  <si>
+    <t>Partial STIR/SHAKEN Implementation - Performing Robocall Mitigation</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=34a57d161b667c10dabd2f41f54bcb14&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004723</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=0df870c21bcdf41002beea82f54bcba2&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005813</t>
-  </si>
-  <si>
-    <t>Glenn Dalgliesh</t>
-  </si>
-  <si>
-    <t>VP of Operations</t>
-  </si>
-  <si>
-    <t>NOC</t>
-  </si>
-  <si>
-    <t>'+14439121000</t>
-  </si>
-  <si>
-    <t>Partial STIR/SHAKEN Implementation - Performing Robocall Mitigation</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=34a57d161b667c10dabd2f41f54bcb14&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0004139</t>
@@ -225,10 +225,32 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b379943f1be37810cc2f2f82f54bcbf5&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0008972</t>
+  </si>
+  <si>
+    <t>Media Flint, Inc.</t>
+  </si>
+  <si>
+    <t>15260 Ventura Boulevard
+Suite 1200 PMB 492
+Sherman Oaks California 91403</t>
+  </si>
+  <si>
+    <t>U.S. Virgin Islands</t>
+  </si>
+  <si>
+    <t>AvidTrak</t>
+  </si>
+  <si>
+    <t>null
+null CA
+California</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=26b57f081b9f74505eb762cfe54bcb14&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0008973</t>
-  </si>
-  <si>
-    <t>Media Flint, Inc.</t>
   </si>
   <si>
     <t>15260 Ventura Boulevard
@@ -236,32 +258,10 @@
 Sherman Oaks CA 91403</t>
   </si>
   <si>
-    <t>U.S. Virgin Islands</t>
-  </si>
-  <si>
-    <t>AvidTrak</t>
-  </si>
-  <si>
-    <t>null
-null CA
-California</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=bfc7bfc81b9f74505eb762cfe54bcbe5&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008972</t>
-  </si>
-  <si>
-    <t>15260 Ventura Boulevard
-Suite 1200 PMB 492
-Sherman Oaks California 91403</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=26b57f081b9f74505eb762cfe54bcb14&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009020</t>
+    <t>RMD0009019</t>
   </si>
   <si>
     <t>Enhanced Telecommunications &amp; Data, Inc.</t>
@@ -277,6 +277,24 @@
     <t>Engineer</t>
   </si>
   <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>208-947-3900</t>
+  </si>
+  <si>
+    <t>3904</t>
+  </si>
+  <si>
+    <t>2024-04-09</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5e6e01191b57f010222b0e9ee54bcb7a&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009020</t>
+  </si>
+  <si>
     <t>IT Department</t>
   </si>
   <si>
@@ -286,25 +304,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=bcd785dd1b17f010222b0e9ee54bcb74&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009019</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>208-947-3900</t>
-  </si>
-  <si>
-    <t>3904</t>
-  </si>
-  <si>
-    <t>2024-04-09</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5e6e01191b57f010222b0e9ee54bcb7a&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009205</t>
+    <t>RMD0009084</t>
   </si>
   <si>
     <t>ADCOM Technologies, LLC</t>
@@ -318,6 +318,12 @@
     <t>ON DEMAND Communications</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fd73904e1b1bf010031f0f21f54bcb87&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009205</t>
+  </si>
+  <si>
     <t>Dean Franks</t>
   </si>
   <si>
@@ -340,13 +346,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=53ad1e731b53b0109294113d9c4bcb6a&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009084</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fd73904e1b1bf010031f0f21f54bcb87&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008869</t>
+    <t>RMD0006774</t>
   </si>
   <si>
     <t>Sage Communications, Inc.</t>
@@ -356,9 +356,18 @@
 Camarillo CA 93012</t>
   </si>
   <si>
+    <t>NONE</t>
+  </si>
+  <si>
     <t>Sage Network &amp; Communications</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612a08851bbef010e1ca848ce54bcbb3&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008869</t>
+  </si>
+  <si>
     <t>Rick Minyard</t>
   </si>
   <si>
@@ -378,15 +387,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ed3d8a531b0334509ac2ea04bc4bcb27&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0006774</t>
-  </si>
-  <si>
-    <t>NONE</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612a08851bbef010e1ca848ce54bcbb3&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0004389</t>
@@ -469,10 +469,20 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1f0635261b85f81002beea82f54bcbec&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0005785</t>
+  </si>
+  <si>
+    <t>Edge Fibernet</t>
+  </si>
+  <si>
+    <t>5004 4th Avenue
+Brooklyn New York 11220</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5dcfb14e1bea3c105e240f6fe54bcb62&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0005786</t>
-  </si>
-  <si>
-    <t>Edge Fibernet</t>
   </si>
   <si>
     <t>254 36th Street
@@ -483,16 +493,6 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=eb20864e1bea3c105e240f6fe54bcbf1&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005785</t>
-  </si>
-  <si>
-    <t>5004 4th Avenue
-Brooklyn New York 11220</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5dcfb14e1bea3c105e240f6fe54bcb62&amp;view=sp</t>
-  </si>
-  <si>
     <t>RMD0007488</t>
   </si>
   <si>
@@ -596,7 +596,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=89cc84f51b4af01068d1a82eac4bcb3e&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004701</t>
+    <t>RMD0003052</t>
   </si>
   <si>
     <t>Jaintel LLC</t>
@@ -606,15 +606,33 @@
 DE 19806-3334 Wilmington, United States</t>
   </si>
   <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
     <t>Elayaraja Jinadoss</t>
   </si>
   <si>
+    <t>Director</t>
+  </si>
+  <si>
+    <t>Management</t>
+  </si>
+  <si>
+    <t>'+447341664829</t>
+  </si>
+  <si>
+    <t>2024-05-01</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=296153731b30b0507ccf20ecac4bcbd8&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004701</t>
+  </si>
+  <si>
     <t>Operations Director</t>
   </si>
   <si>
-    <t>Management</t>
-  </si>
-  <si>
     <t>'+1 737 237 0913</t>
   </si>
   <si>
@@ -622,24 +640,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b1f3904a1b4138107ccf20ecac4bcbbf&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0003052</t>
-  </si>
-  <si>
-    <t>United Kingdom</t>
-  </si>
-  <si>
-    <t>Director</t>
-  </si>
-  <si>
-    <t>'+447341664829</t>
-  </si>
-  <si>
-    <t>2024-05-01</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=296153731b30b0507ccf20ecac4bcbd8&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0003053</t>
@@ -670,7 +670,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1e7857331b4885103e8aa93be54bcb79&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0003444</t>
+    <t>RMD0003442</t>
   </si>
   <si>
     <t>Shaw Telecom GP</t>
@@ -681,32 +681,6 @@
   </si>
   <si>
     <t>Canada</t>
-  </si>
-  <si>
-    <t>0031064868; 0031064884; 0031064900</t>
-  </si>
-  <si>
-    <t>SHAW CORP; 1503357 Alberta Ltd.; 1950036 Ontario Ltd.; Mid-Bowline Group Corp.; Mid-Bowline Holdings Corp.; Wind Mobile Corp.; Freedom Mobile Inc.</t>
-  </si>
-  <si>
-    <t>Network Operations</t>
-  </si>
-  <si>
-    <t>TOPS-NR&amp;A</t>
-  </si>
-  <si>
-    <t>2728 Hopewell Place N.E.
-Calgary AE 17724
-Alberta</t>
-  </si>
-  <si>
-    <t>'+1-866-244-7475</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5d9f0e581b8df0509294113d9c4bcb95&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0003442</t>
   </si>
   <si>
     <t>0031064868;
@@ -726,6 +700,32 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=322c4e941b8df0509294113d9c4bcb51&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0003444</t>
+  </si>
+  <si>
+    <t>0031064868; 0031064884; 0031064900</t>
+  </si>
+  <si>
+    <t>SHAW CORP; 1503357 Alberta Ltd.; 1950036 Ontario Ltd.; Mid-Bowline Group Corp.; Mid-Bowline Holdings Corp.; Wind Mobile Corp.; Freedom Mobile Inc.</t>
+  </si>
+  <si>
+    <t>Network Operations</t>
+  </si>
+  <si>
+    <t>TOPS-NR&amp;A</t>
+  </si>
+  <si>
+    <t>2728 Hopewell Place N.E.
+Calgary AE 17724
+Alberta</t>
+  </si>
+  <si>
+    <t>'+1-866-244-7475</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5d9f0e581b8df0509294113d9c4bcb95&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0007384</t>
   </si>
   <si>
@@ -754,7 +754,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=76af51511bc9f0102eb2a82fe54bcb18&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008577</t>
+    <t>RMD0005040</t>
   </si>
   <si>
     <t>Dialect, LLC</t>
@@ -764,6 +764,12 @@
 Phoenix AZ 85008</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f58908e11b793c10680f657ae54bcb6d&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008577</t>
+  </si>
+  <si>
     <t>BatchDialer</t>
   </si>
   <si>
@@ -780,12 +786,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ee4909b01b8f7c10aa3cea41f54bcb77&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005040</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f58908e11b793c10680f657ae54bcb6d&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0005569</t>
@@ -836,7 +836,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612913461bd6f010ca5aec21f54bcbac&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007936</t>
+    <t>RMD0005297</t>
   </si>
   <si>
     <t>STREAMLINE SELLERS PTY LTD</t>
@@ -849,6 +849,12 @@
     <t>Australia</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d24a9a271bca3810d49ca86ce54bcb20&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007936</t>
+  </si>
+  <si>
     <t>Syed Omar Farooq Shah</t>
   </si>
   <si>
@@ -858,13 +864,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6273a2321b3638109ac2ea04bc4bcb55&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005297</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d24a9a271bca3810d49ca86ce54bcb20&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005585</t>
+    <t>RMD0005574</t>
   </si>
   <si>
     <t>MegaClec, Inc</t>
@@ -878,6 +878,22 @@
     <t>0012465480</t>
   </si>
   <si>
+    <t>Troy City Internet Exchange;Voiceway;Meganet Communications</t>
+  </si>
+  <si>
+    <t>187 Plymouth Ave
+Fall River MA 02721</t>
+  </si>
+  <si>
+    <t>5086460030</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1426e7581ba678109294113d9c4bcb2f&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005585</t>
+  </si>
+  <si>
     <t>Voiceay, Voiceway Netoworks, Meganet,  Troy City Internet Exchange</t>
   </si>
   <si>
@@ -891,23 +907,7 @@
 Fall River MA 02721</t>
   </si>
   <si>
-    <t>5086460030</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c9f5735c1ba2781002beea82f54bcbaf&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005574</t>
-  </si>
-  <si>
-    <t>Troy City Internet Exchange;Voiceway;Meganet Communications</t>
-  </si>
-  <si>
-    <t>187 Plymouth Ave
-Fall River MA 02721</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1426e7581ba678109294113d9c4bcb2f&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0007962</t>
@@ -993,7 +993,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=cfeb296a1bf6f410680f657ae54bcbeb&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007696</t>
+    <t>RMD0007716</t>
   </si>
   <si>
     <t>High Country Internet</t>
@@ -1003,16 +1003,16 @@
 Tucson AZ 85719</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=4a516ea21b7ef410165aedfde54bcbd3&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007696</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=e3d356aa1b3ef410165aedfde54bcb51&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007716</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=4a516ea21b7ef410165aedfde54bcbd3&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007944</t>
+    <t>RMD0007939</t>
   </si>
   <si>
     <t>Conquest Solutions</t>
@@ -1022,6 +1022,12 @@
 Marietta GA 30067</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d225a2fe1b7a3810e4ccdb1de54bcbff&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007944</t>
+  </si>
+  <si>
     <t>Lance Retter</t>
   </si>
   <si>
@@ -1035,12 +1041,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c186e6321bba3810e4ccdb1de54bcb5a&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007939</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d225a2fe1b7a3810e4ccdb1de54bcbff&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008423</t>
@@ -1074,7 +1074,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=545854ef1b7ab810d39dddb6bc4bcb74&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008451</t>
+    <t>RMD0008450</t>
   </si>
   <si>
     <t>WTS</t>
@@ -1084,12 +1084,6 @@
 Greensboro NC 27401</t>
   </si>
   <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d7e7ad2b1bbeb81093d3a820f54bcb5c&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008450</t>
-  </si>
-  <si>
     <t>null
 null NC</t>
   </si>
@@ -1097,6 +1091,12 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b746a9e71bbeb81093d3a820f54bcb4c&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0008451</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d7e7ad2b1bbeb81093d3a820f54bcb5c&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0008611</t>
   </si>
   <si>
@@ -1116,25 +1116,25 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8ce1e5851b0bbc1093d3a820f54bcba5&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0008612</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Bharat Raj</t>
+  </si>
+  <si>
+    <t>'+919836963636</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=21f229c51b0bbc1093d3a820f54bcbdb&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0008610</t>
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9c9129851b0bbc1093d3a820f54bcb97&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008612</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>Bharat Raj</t>
-  </si>
-  <si>
-    <t>'+919836963636</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=21f229c51b0bbc1093d3a820f54bcbdb&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008759</t>
@@ -6314,16 +6314,28 @@
         <v>46</v>
       </c>
       <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
+      <c r="J5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="M5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
+        <v>44</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
+      <c r="Q5" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="R5" s="1" t="s">
         <v>26</v>
       </c>
@@ -6331,16 +6343,16 @@
         <v>26</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B6" s="1">
         <v>17118795</v>
@@ -6364,28 +6376,16 @@
         <v>46</v>
       </c>
       <c r="I6" s="1"/>
-      <c r="J6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
       <c r="M6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>52</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
       <c r="P6" s="1"/>
-      <c r="Q6" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="Q6" s="1"/>
       <c r="R6" s="1" t="s">
         <v>26</v>
       </c>
@@ -6393,7 +6393,7 @@
         <v>26</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U6" s="1"/>
       <c r="V6" s="1" t="s">
@@ -6662,9 +6662,11 @@
       <c r="O11" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="P11" s="1"/>
+      <c r="P11" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="Q11" s="1" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="R11" s="1" t="s">
         <v>30</v>
@@ -6675,14 +6677,16 @@
       <c r="T11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U11" s="1"/>
+      <c r="U11" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="V11" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B12" s="1">
         <v>21520390</v>
@@ -6709,7 +6713,7 @@
         <v>82</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>80</v>
@@ -6718,13 +6722,11 @@
         <v>27</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>89</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="P12" s="1"/>
       <c r="Q12" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="R12" s="1" t="s">
         <v>30</v>
@@ -6735,9 +6737,7 @@
       <c r="T12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U12" s="1" t="s">
-        <v>90</v>
-      </c>
+      <c r="U12" s="1"/>
       <c r="V12" s="1" t="s">
         <v>91</v>
       </c>
@@ -6756,55 +6756,41 @@
         <v>94</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
         <v>95</v>
       </c>
       <c r="I13" s="1"/>
-      <c r="J13" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>100</v>
-      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
       <c r="P13" s="1"/>
-      <c r="Q13" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q13" s="1"/>
       <c r="R13" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S13" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U13" s="1"/>
       <c r="V13" s="1" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B14" s="1">
         <v>23003460</v>
@@ -6816,32 +6802,46 @@
         <v>94</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
         <v>95</v>
       </c>
       <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
+      <c r="J14" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="P14" s="1"/>
-      <c r="Q14" s="1"/>
+      <c r="Q14" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="R14" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S14" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U14" s="1"/>
       <c r="V14" s="1" t="s">
@@ -6867,54 +6867,40 @@
       <c r="F15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G15" s="1"/>
+      <c r="G15" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="H15" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I15" s="1"/>
-      <c r="J15" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="K15" s="1" t="s">
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="V15" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B16" s="1">
         <v>23250467</v>
@@ -6931,33 +6917,47 @@
       <c r="F16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="1"/>
+      <c r="H16" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U16" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U16" s="1"/>
       <c r="V16" s="1" t="s">
         <v>118</v>
       </c>
@@ -7123,13 +7123,13 @@
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L20" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>127</v>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="P20" s="1"/>
       <c r="Q20" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R20" s="1" t="s">
         <v>26</v>
@@ -7460,7 +7460,7 @@
       </c>
       <c r="P26" s="1"/>
       <c r="Q26" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R26" s="1" t="s">
         <v>26</v>
@@ -7608,55 +7608,61 @@
         <v>184</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
+        <v>185</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="J29" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>184</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P29" s="1"/>
       <c r="Q29" s="1" t="s">
         <v>39</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="T29" s="1" t="s">
         <v>26</v>
       </c>
       <c r="U29" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="V29" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="A30" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B30" s="1">
         <v>30758643</v>
@@ -7668,34 +7674,28 @@
         <v>184</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>117</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
       <c r="J30" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>193</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>184</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>192</v>
+        <v>27</v>
       </c>
       <c r="O30" s="1" t="s">
         <v>194</v>
@@ -7705,10 +7705,10 @@
         <v>39</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="T30" s="1" t="s">
         <v>26</v>
@@ -7737,7 +7737,7 @@
         <v>30</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
@@ -7783,7 +7783,7 @@
         <v>30</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
@@ -7801,14 +7801,14 @@
         <v>199</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O32" s="1" t="s">
         <v>204</v>
       </c>
       <c r="P32" s="1"/>
       <c r="Q32" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R32" s="1" t="s">
         <v>30</v>
@@ -7850,45 +7850,33 @@
       <c r="I33" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="J33" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>213</v>
-      </c>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
       <c r="M33" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="O33" s="1" t="s">
-        <v>215</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
       <c r="P33" s="1"/>
-      <c r="Q33" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q33" s="1"/>
       <c r="R33" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S33" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U33" s="1"/>
       <c r="V33" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="34" spans="1:22">
       <c r="A34" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B34" s="1">
         <v>31064850</v>
@@ -7906,30 +7894,42 @@
         <v>209</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="O34" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
       <c r="P34" s="1"/>
-      <c r="Q34" s="1"/>
+      <c r="Q34" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="R34" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S34" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U34" s="1"/>
       <c r="V34" s="1" t="s">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="P35" s="1"/>
       <c r="Q35" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R35" s="1" t="s">
         <v>30</v>
@@ -8061,48 +8061,34 @@
       </c>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
-      <c r="I37" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>236</v>
-      </c>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
       <c r="M37" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O37" s="1" t="s">
-        <v>237</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
       <c r="P37" s="1"/>
-      <c r="Q37" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="Q37" s="1"/>
       <c r="R37" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S37" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U37" s="1"/>
       <c r="V37" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="38" spans="1:22">
       <c r="A38" s="1" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B38" s="1">
         <v>31124688</v>
@@ -8121,25 +8107,39 @@
       </c>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
+      <c r="I38" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>238</v>
+      </c>
       <c r="M38" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
+        <v>232</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>239</v>
+      </c>
       <c r="P38" s="1"/>
-      <c r="Q38" s="1"/>
+      <c r="Q38" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="R38" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S38" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U38" s="1"/>
       <c r="V38" s="1" t="s">
@@ -8188,7 +8188,7 @@
       </c>
       <c r="P39" s="1"/>
       <c r="Q39" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R39" s="1" t="s">
         <v>26</v>
@@ -8290,45 +8290,33 @@
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
-      <c r="J41" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="L41" s="1" t="s">
-        <v>203</v>
-      </c>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
       <c r="M41" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="N41" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="O41" s="1" t="s">
-        <v>261</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
       <c r="P41" s="1"/>
-      <c r="Q41" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q41" s="1"/>
       <c r="R41" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S41" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U41" s="1"/>
       <c r="V41" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="42" spans="1:22">
       <c r="A42" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B42" s="1">
         <v>31294614</v>
@@ -8348,24 +8336,36 @@
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
+      <c r="J42" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>203</v>
+      </c>
       <c r="M42" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N42" s="1"/>
-      <c r="O42" s="1"/>
+        <v>258</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>263</v>
+      </c>
       <c r="P42" s="1"/>
-      <c r="Q42" s="1"/>
+      <c r="Q42" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="R42" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U42" s="1"/>
       <c r="V42" s="1" t="s">
@@ -8397,48 +8397,42 @@
       <c r="H43" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1" t="s">
+      <c r="I43" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="K43" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="L43" s="1" t="s">
+      <c r="N43" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O43" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="M43" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="N43" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O43" s="1" t="s">
-        <v>273</v>
       </c>
       <c r="P43" s="1"/>
       <c r="Q43" s="1" t="s">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="R43" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U43" s="1" t="s">
-        <v>62</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="U43" s="1"/>
       <c r="V43" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="44" spans="1:22">
       <c r="A44" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B44" s="1">
         <v>31356652</v>
@@ -8459,14 +8453,18 @@
         <v>268</v>
       </c>
       <c r="H44" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L44" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="I44" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
       <c r="M44" s="1" t="s">
         <v>277</v>
       </c>
@@ -8474,22 +8472,24 @@
         <v>27</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="P44" s="1"/>
       <c r="Q44" s="1" t="s">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S44" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U44" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="U44" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="V44" s="1" t="s">
         <v>278</v>
       </c>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="P45" s="1"/>
       <c r="Q45" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R45" s="1" t="s">
         <v>30</v>
@@ -8815,9 +8815,15 @@
       <c r="F51" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
+      <c r="G51" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
@@ -8861,15 +8867,9 @@
       <c r="F52" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G52" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I52" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
@@ -8908,55 +8908,41 @@
         <v>313</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
-      <c r="J53" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="L53" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
       <c r="M53" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="N53" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O53" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="P53" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="Q53" s="1" t="s">
-        <v>39</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N53" s="1"/>
+      <c r="O53" s="1"/>
+      <c r="P53" s="1"/>
+      <c r="Q53" s="1"/>
       <c r="R53" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S53" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U53" s="1"/>
       <c r="V53" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
     <row r="54" spans="1:22">
       <c r="A54" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B54" s="1">
         <v>31445216</v>
@@ -8968,32 +8954,46 @@
         <v>313</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
-      <c r="L54" s="1"/>
+      <c r="J54" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="M54" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N54" s="1"/>
-      <c r="O54" s="1"/>
-      <c r="P54" s="1"/>
-      <c r="Q54" s="1"/>
+        <v>313</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="P54" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q54" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="R54" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S54" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U54" s="1"/>
       <c r="V54" s="1" t="s">
@@ -9128,7 +9128,7 @@
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
       <c r="M57" s="1" t="s">
-        <v>29</v>
+        <v>333</v>
       </c>
       <c r="N57" s="1"/>
       <c r="O57" s="1"/>
@@ -9145,12 +9145,12 @@
       </c>
       <c r="U57" s="1"/>
       <c r="V57" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="58" spans="1:22">
       <c r="A58" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B58" s="1">
         <v>31457815</v>
@@ -9174,7 +9174,7 @@
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="1" t="s">
-        <v>335</v>
+        <v>29</v>
       </c>
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
@@ -9259,38 +9259,50 @@
         <v>30</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
-      <c r="J60" s="1"/>
-      <c r="K60" s="1"/>
-      <c r="L60" s="1"/>
+      <c r="J60" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="M60" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N60" s="1"/>
-      <c r="O60" s="1"/>
+        <v>339</v>
+      </c>
+      <c r="N60" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>346</v>
+      </c>
       <c r="P60" s="1"/>
-      <c r="Q60" s="1"/>
+      <c r="Q60" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="R60" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S60" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U60" s="1"/>
       <c r="V60" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="61" spans="1:22">
       <c r="A61" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B61" s="1">
         <v>31475270</v>
@@ -9305,41 +9317,29 @@
         <v>30</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
-      <c r="J61" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="L61" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
       <c r="M61" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="N61" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="O61" s="1" t="s">
-        <v>348</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N61" s="1"/>
+      <c r="O61" s="1"/>
       <c r="P61" s="1"/>
-      <c r="Q61" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q61" s="1"/>
       <c r="R61" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S61" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U61" s="1"/>
       <c r="V61" s="1" t="s">
@@ -9386,7 +9386,7 @@
         <v>354</v>
       </c>
       <c r="Q62" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R62" s="1" t="s">
         <v>30</v>
@@ -9492,7 +9492,7 @@
         <v>366</v>
       </c>
       <c r="Q64" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R64" s="1" t="s">
         <v>30</v>
@@ -9850,7 +9850,7 @@
       </c>
       <c r="P71" s="1"/>
       <c r="Q71" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R71" s="1" t="s">
         <v>30</v>
@@ -9952,7 +9952,7 @@
       </c>
       <c r="P73" s="1"/>
       <c r="Q73" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R73" s="1" t="s">
         <v>30</v>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="P75" s="1"/>
       <c r="Q75" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R75" s="1" t="s">
         <v>30</v>
@@ -10151,7 +10151,7 @@
         <v>30</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G77" s="1"/>
       <c r="H77" s="1"/>
@@ -10220,7 +10220,7 @@
         <v>430</v>
       </c>
       <c r="Q78" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R78" s="1" t="s">
         <v>26</v>
@@ -10258,7 +10258,7 @@
         <v>434</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J79" s="1" t="s">
         <v>435</v>
@@ -10280,7 +10280,7 @@
       </c>
       <c r="P79" s="1"/>
       <c r="Q79" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R79" s="1" t="s">
         <v>30</v>
@@ -10338,7 +10338,7 @@
       </c>
       <c r="P80" s="1"/>
       <c r="Q80" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R80" s="1" t="s">
         <v>30</v>
@@ -10458,7 +10458,7 @@
         <v>459</v>
       </c>
       <c r="Q82" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R82" s="1" t="s">
         <v>26</v>
@@ -10551,7 +10551,7 @@
         <v>245</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M84" s="1" t="s">
         <v>465</v>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="P84" s="1"/>
       <c r="Q84" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R84" s="1" t="s">
         <v>30</v>
@@ -11044,7 +11044,7 @@
       </c>
       <c r="P93" s="1"/>
       <c r="Q93" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R93" s="1" t="s">
         <v>30</v>
@@ -11089,7 +11089,7 @@
         <v>523</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="M94" s="1" t="s">
         <v>520</v>
@@ -11156,7 +11156,7 @@
       </c>
       <c r="P95" s="1"/>
       <c r="Q95" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R95" s="1" t="s">
         <v>30</v>
@@ -11318,7 +11318,7 @@
       </c>
       <c r="P98" s="1"/>
       <c r="Q98" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R98" s="1" t="s">
         <v>30</v>
@@ -11397,7 +11397,7 @@
         <v>30</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G100" s="1" t="s">
         <v>28</v>
@@ -11443,7 +11443,7 @@
         <v>30</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G101" s="1"/>
       <c r="H101" s="1"/>
@@ -11516,7 +11516,7 @@
       </c>
       <c r="P102" s="1"/>
       <c r="Q102" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R102" s="1" t="s">
         <v>30</v>
@@ -11550,13 +11550,13 @@
         <v>27</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J103" s="1" t="s">
         <v>564</v>
@@ -11565,7 +11565,7 @@
         <v>59</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M103" s="1" t="s">
         <v>563</v>
@@ -11578,7 +11578,7 @@
       </c>
       <c r="P103" s="1"/>
       <c r="Q103" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R103" s="1" t="s">
         <v>30</v>
@@ -11640,7 +11640,7 @@
       </c>
       <c r="P104" s="1"/>
       <c r="Q104" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R104" s="1" t="s">
         <v>26</v>
@@ -12216,13 +12216,13 @@
         <v>27</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J115" s="1" t="s">
         <v>637</v>
@@ -12304,7 +12304,7 @@
       </c>
       <c r="P116" s="1"/>
       <c r="Q116" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R116" s="1" t="s">
         <v>26</v>
@@ -12353,7 +12353,7 @@
         <v>655</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M117" s="1" t="s">
         <v>650</v>
@@ -12409,7 +12409,7 @@
         <v>59</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M118" s="1" t="s">
         <v>659</v>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="P124" s="1"/>
       <c r="Q124" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R124" s="1" t="s">
         <v>30</v>
@@ -12916,10 +12916,10 @@
         <v>718</v>
       </c>
       <c r="K127" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M127" s="1" t="s">
         <v>717</v>
@@ -12932,7 +12932,7 @@
       </c>
       <c r="P127" s="1"/>
       <c r="Q127" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R127" s="1" t="s">
         <v>30</v>
@@ -13046,7 +13046,7 @@
       </c>
       <c r="P129" s="1"/>
       <c r="Q129" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R129" s="1" t="s">
         <v>30</v>
@@ -13141,7 +13141,7 @@
         <v>30</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G131" s="1" t="s">
         <v>28</v>
@@ -13165,7 +13165,7 @@
         <v>741</v>
       </c>
       <c r="N131" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O131" s="1" t="s">
         <v>744</v>
@@ -13230,7 +13230,7 @@
       </c>
       <c r="P132" s="1"/>
       <c r="Q132" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R132" s="1" t="s">
         <v>30</v>
@@ -13273,7 +13273,7 @@
         <v>755</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M133" s="1" t="s">
         <v>753</v>
@@ -13331,7 +13331,7 @@
         <v>245</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M134" s="1" t="s">
         <v>759</v>
@@ -13387,7 +13387,7 @@
         <v>768</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M135" s="1" t="s">
         <v>765</v>
@@ -13458,7 +13458,7 @@
       </c>
       <c r="P136" s="1"/>
       <c r="Q136" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R136" s="1" t="s">
         <v>30</v>
@@ -13578,7 +13578,7 @@
       </c>
       <c r="P138" s="1"/>
       <c r="Q138" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R138" s="1" t="s">
         <v>30</v>
@@ -13658,13 +13658,13 @@
         <v>27</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H140" s="1" t="s">
         <v>797</v>
       </c>
       <c r="I140" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J140" s="1" t="s">
         <v>798</v>
@@ -13673,7 +13673,7 @@
         <v>799</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M140" s="1" t="s">
         <v>796</v>
@@ -13854,7 +13854,7 @@
       </c>
       <c r="P143" s="1"/>
       <c r="Q143" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R143" s="1" t="s">
         <v>30</v>
@@ -14017,7 +14017,7 @@
         <v>840</v>
       </c>
       <c r="L146" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M146" s="1" t="s">
         <v>841</v>
@@ -14061,7 +14061,7 @@
         <v>30</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G147" s="1"/>
       <c r="H147" s="1"/>
@@ -14079,14 +14079,14 @@
         <v>847</v>
       </c>
       <c r="N147" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O147" s="1" t="s">
         <v>848</v>
       </c>
       <c r="P147" s="1"/>
       <c r="Q147" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R147" s="1" t="s">
         <v>30</v>
@@ -14115,7 +14115,7 @@
         <v>30</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G148" s="1" t="s">
         <v>851</v>
@@ -14188,7 +14188,7 @@
       </c>
       <c r="P149" s="1"/>
       <c r="Q149" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R149" s="1" t="s">
         <v>30</v>
@@ -14242,7 +14242,7 @@
       </c>
       <c r="P150" s="1"/>
       <c r="Q150" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R150" s="1" t="s">
         <v>30</v>
@@ -14406,7 +14406,7 @@
         <v>885</v>
       </c>
       <c r="Q153" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R153" s="1" t="s">
         <v>26</v>
@@ -14598,7 +14598,7 @@
       </c>
       <c r="P157" s="1"/>
       <c r="Q157" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R157" s="1" t="s">
         <v>30</v>
@@ -14643,7 +14643,7 @@
         <v>907</v>
       </c>
       <c r="L158" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M158" s="1"/>
       <c r="N158" s="1" t="s">
@@ -14696,7 +14696,7 @@
         <v>913</v>
       </c>
       <c r="K159" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L159" s="1" t="s">
         <v>914</v>
@@ -14806,7 +14806,7 @@
       </c>
       <c r="P161" s="1"/>
       <c r="Q161" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R161" s="1" t="s">
         <v>26</v>
@@ -14849,7 +14849,7 @@
         <v>59</v>
       </c>
       <c r="L162" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M162" s="1"/>
       <c r="N162" s="1" t="s">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="P162" s="1"/>
       <c r="Q162" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R162" s="1" t="s">
         <v>30</v>
@@ -14933,7 +14933,7 @@
         <v>30</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G164" s="1"/>
       <c r="H164" s="1"/>
@@ -14942,21 +14942,21 @@
         <v>937</v>
       </c>
       <c r="K164" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L164" s="1" t="s">
         <v>203</v>
       </c>
       <c r="M164" s="1"/>
       <c r="N164" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O164" s="1" t="s">
         <v>938</v>
       </c>
       <c r="P164" s="1"/>
       <c r="Q164" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R164" s="1" t="s">
         <v>30</v>
@@ -15068,7 +15068,7 @@
       </c>
       <c r="P166" s="1"/>
       <c r="Q166" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R166" s="1" t="s">
         <v>30</v>
@@ -15128,7 +15128,7 @@
       </c>
       <c r="P167" s="1"/>
       <c r="Q167" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R167" s="1" t="s">
         <v>30</v>
@@ -15190,7 +15190,7 @@
       </c>
       <c r="P168" s="1"/>
       <c r="Q168" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R168" s="1" t="s">
         <v>30</v>
@@ -15273,7 +15273,7 @@
         <v>30</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G170" s="1"/>
       <c r="H170" s="1"/>
@@ -15285,11 +15285,11 @@
         <v>59</v>
       </c>
       <c r="L170" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M170" s="1"/>
       <c r="N170" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O170" s="1" t="s">
         <v>974</v>
@@ -15330,7 +15330,7 @@
         <v>27</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H171" s="1" t="s">
         <v>978</v>
@@ -15358,7 +15358,7 @@
       </c>
       <c r="P171" s="1"/>
       <c r="Q171" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R171" s="1" t="s">
         <v>30</v>
@@ -15389,7 +15389,7 @@
         <v>30</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G172" s="1" t="s">
         <v>28</v>
@@ -15413,14 +15413,14 @@
         <v>987</v>
       </c>
       <c r="N172" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O172" s="1" t="s">
         <v>988</v>
       </c>
       <c r="P172" s="1"/>
       <c r="Q172" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R172" s="1" t="s">
         <v>30</v>
@@ -15478,7 +15478,7 @@
       </c>
       <c r="P173" s="1"/>
       <c r="Q173" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R173" s="1" t="s">
         <v>26</v>
@@ -15512,7 +15512,7 @@
         <v>27</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H174" s="1"/>
       <c r="I174" s="1"/>
@@ -15615,7 +15615,7 @@
         <v>1007</v>
       </c>
       <c r="L176" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M176" s="1"/>
       <c r="N176" s="1" t="s">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="P181" s="1"/>
       <c r="Q181" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R181" s="1" t="s">
         <v>30</v>
@@ -16123,7 +16123,7 @@
         <v>293</v>
       </c>
       <c r="L185" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M185" s="1" t="s">
         <v>1057</v>
@@ -16226,13 +16226,13 @@
         <v>27</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H187" s="1" t="s">
         <v>1067</v>
       </c>
       <c r="I187" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J187" s="1"/>
       <c r="K187" s="1"/>
@@ -16358,7 +16358,7 @@
       </c>
       <c r="P189" s="1"/>
       <c r="Q189" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R189" s="1" t="s">
         <v>30</v>
@@ -16387,7 +16387,7 @@
         <v>30</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G190" s="1"/>
       <c r="H190" s="1"/>
@@ -16396,21 +16396,21 @@
         <v>1084</v>
       </c>
       <c r="K190" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L190" s="1" t="s">
         <v>1085</v>
       </c>
       <c r="M190" s="1"/>
       <c r="N190" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O190" s="1" t="s">
         <v>1086</v>
       </c>
       <c r="P190" s="1"/>
       <c r="Q190" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R190" s="1" t="s">
         <v>30</v>
@@ -16468,7 +16468,7 @@
       </c>
       <c r="P191" s="1"/>
       <c r="Q191" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R191" s="1" t="s">
         <v>26</v>
@@ -16526,7 +16526,7 @@
       </c>
       <c r="P192" s="1"/>
       <c r="Q192" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R192" s="1" t="s">
         <v>26</v>
@@ -16573,7 +16573,7 @@
         <v>1106</v>
       </c>
       <c r="L193" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M193" s="1" t="s">
         <v>1107</v>
@@ -16586,7 +16586,7 @@
       </c>
       <c r="P193" s="1"/>
       <c r="Q193" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R193" s="1" t="s">
         <v>30</v>
@@ -16617,7 +16617,7 @@
         <v>30</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G194" s="1"/>
       <c r="H194" s="1"/>
@@ -16635,14 +16635,14 @@
         <v>1114</v>
       </c>
       <c r="N194" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O194" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="P194" s="1"/>
       <c r="Q194" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R194" s="1" t="s">
         <v>30</v>
@@ -16805,7 +16805,7 @@
         <v>59</v>
       </c>
       <c r="L197" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M197" s="1" t="s">
         <v>1135</v>
@@ -16818,7 +16818,7 @@
       </c>
       <c r="P197" s="1"/>
       <c r="Q197" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R197" s="1" t="s">
         <v>30</v>
@@ -16880,7 +16880,7 @@
       </c>
       <c r="P198" s="1"/>
       <c r="Q198" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R198" s="1" t="s">
         <v>30</v>
@@ -16975,7 +16975,7 @@
         <v>30</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G200" s="1"/>
       <c r="H200" s="1"/>
@@ -16987,18 +16987,18 @@
         <v>474</v>
       </c>
       <c r="L200" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M200" s="1"/>
       <c r="N200" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O200" s="1" t="s">
         <v>1158</v>
       </c>
       <c r="P200" s="1"/>
       <c r="Q200" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R200" s="1" t="s">
         <v>30</v>
@@ -17047,7 +17047,7 @@
         <v>165</v>
       </c>
       <c r="L201" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M201" s="1" t="s">
         <v>1166</v>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="P201" s="1"/>
       <c r="Q201" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R201" s="1" t="s">
         <v>30</v>
@@ -17366,13 +17366,13 @@
         <v>27</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H207" s="1" t="s">
         <v>1197</v>
       </c>
       <c r="I207" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J207" s="1"/>
       <c r="K207" s="1"/>
@@ -17426,7 +17426,7 @@
         <v>1203</v>
       </c>
       <c r="K208" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L208" s="1" t="s">
         <v>1204</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="P209" s="1"/>
       <c r="Q209" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R209" s="1" t="s">
         <v>30</v>
@@ -17560,7 +17560,7 @@
       </c>
       <c r="P210" s="1"/>
       <c r="Q210" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R210" s="1" t="s">
         <v>30</v>
@@ -17620,7 +17620,7 @@
       </c>
       <c r="P211" s="1"/>
       <c r="Q211" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R211" s="1" t="s">
         <v>30</v>
@@ -17666,7 +17666,7 @@
         <v>1237</v>
       </c>
       <c r="K212" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L212" s="1" t="s">
         <v>1238</v>
@@ -17682,7 +17682,7 @@
       </c>
       <c r="P212" s="1"/>
       <c r="Q212" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R212" s="1" t="s">
         <v>30</v>
@@ -17732,7 +17732,7 @@
         <v>1237</v>
       </c>
       <c r="K213" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L213" s="1" t="s">
         <v>1238</v>
@@ -17748,7 +17748,7 @@
       </c>
       <c r="P213" s="1"/>
       <c r="Q213" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R213" s="1" t="s">
         <v>30</v>
@@ -17783,16 +17783,16 @@
         <v>30</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H214" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I214" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J214" s="1" t="s">
         <v>1252</v>
@@ -17807,7 +17807,7 @@
         <v>1251</v>
       </c>
       <c r="N214" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O214" s="1" t="s">
         <v>1254</v>
@@ -17849,7 +17849,7 @@
         <v>30</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G215" s="1" t="s">
         <v>1257</v>
@@ -17869,7 +17869,7 @@
         <v>1251</v>
       </c>
       <c r="N215" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O215" s="1" t="s">
         <v>1254</v>
@@ -17984,10 +17984,10 @@
         <v>1271</v>
       </c>
       <c r="K217" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L217" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M217" s="1" t="s">
         <v>1272</v>
@@ -18062,7 +18062,7 @@
       </c>
       <c r="P218" s="1"/>
       <c r="Q218" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R218" s="1" t="s">
         <v>30</v>
@@ -18122,7 +18122,7 @@
       </c>
       <c r="P219" s="1"/>
       <c r="Q219" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R219" s="1" t="s">
         <v>30</v>
@@ -18158,7 +18158,7 @@
         <v>1201</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H220" s="1"/>
       <c r="I220" s="1"/>
@@ -18182,7 +18182,7 @@
       </c>
       <c r="P220" s="1"/>
       <c r="Q220" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R220" s="1" t="s">
         <v>30</v>
@@ -18272,7 +18272,7 @@
         <v>1296</v>
       </c>
       <c r="K222" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L222" s="1" t="s">
         <v>203</v>
@@ -18401,7 +18401,7 @@
         <v>1309</v>
       </c>
       <c r="L224" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M224" s="1" t="s">
         <v>1310</v>
@@ -18461,7 +18461,7 @@
         <v>1317</v>
       </c>
       <c r="L225" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M225" s="1" t="s">
         <v>1318</v>
@@ -18474,7 +18474,7 @@
       </c>
       <c r="P225" s="1"/>
       <c r="Q225" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R225" s="1" t="s">
         <v>30</v>
@@ -18532,7 +18532,7 @@
       </c>
       <c r="P226" s="1"/>
       <c r="Q226" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R226" s="1" t="s">
         <v>26</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="P227" s="1"/>
       <c r="Q227" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R227" s="1" t="s">
         <v>26</v>
@@ -18652,7 +18652,7 @@
       </c>
       <c r="P228" s="1"/>
       <c r="Q228" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R228" s="1" t="s">
         <v>30</v>
@@ -18716,7 +18716,7 @@
       </c>
       <c r="P229" s="1"/>
       <c r="Q229" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R229" s="1" t="s">
         <v>30</v>
@@ -18780,7 +18780,7 @@
       </c>
       <c r="P230" s="1"/>
       <c r="Q230" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R230" s="1" t="s">
         <v>30</v>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="P233" s="1"/>
       <c r="Q233" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R233" s="1" t="s">
         <v>30</v>
@@ -19013,7 +19013,7 @@
         <v>165</v>
       </c>
       <c r="L234" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M234" s="1" t="s">
         <v>1383</v>
@@ -19026,7 +19026,7 @@
       </c>
       <c r="P234" s="1"/>
       <c r="Q234" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R234" s="1" t="s">
         <v>30</v>
@@ -19064,13 +19064,13 @@
         <v>27</v>
       </c>
       <c r="G235" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H235" s="1" t="s">
         <v>1388</v>
       </c>
       <c r="I235" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J235" s="1" t="s">
         <v>1389</v>
@@ -19092,7 +19092,7 @@
       </c>
       <c r="P235" s="1"/>
       <c r="Q235" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R235" s="1" t="s">
         <v>30</v>
@@ -19211,7 +19211,7 @@
         <v>768</v>
       </c>
       <c r="L237" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M237" s="1" t="s">
         <v>1406</v>
@@ -19224,7 +19224,7 @@
       </c>
       <c r="P237" s="1"/>
       <c r="Q237" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R237" s="1" t="s">
         <v>30</v>
@@ -19290,7 +19290,7 @@
       </c>
       <c r="P238" s="1"/>
       <c r="Q238" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R238" s="1" t="s">
         <v>30</v>
@@ -19338,7 +19338,7 @@
         <v>1422</v>
       </c>
       <c r="K239" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L239" s="1" t="s">
         <v>1423</v>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="P239" s="1"/>
       <c r="Q239" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R239" s="1" t="s">
         <v>30</v>
@@ -19418,7 +19418,7 @@
       </c>
       <c r="P240" s="1"/>
       <c r="Q240" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R240" s="1" t="s">
         <v>30</v>
@@ -19476,7 +19476,7 @@
       </c>
       <c r="P241" s="1"/>
       <c r="Q241" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R241" s="1" t="s">
         <v>30</v>
@@ -19724,7 +19724,7 @@
       </c>
       <c r="P245" s="1"/>
       <c r="Q245" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R245" s="1" t="s">
         <v>30</v>
@@ -19839,7 +19839,7 @@
         <v>1475</v>
       </c>
       <c r="L247" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M247" s="1" t="s">
         <v>1480</v>
@@ -19912,7 +19912,7 @@
       </c>
       <c r="P248" s="1"/>
       <c r="Q248" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R248" s="1" t="s">
         <v>26</v>
@@ -19956,10 +19956,10 @@
         <v>1491</v>
       </c>
       <c r="K249" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L249" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="M249" s="1" t="s">
         <v>1490</v>
@@ -19972,7 +19972,7 @@
       </c>
       <c r="P249" s="1"/>
       <c r="Q249" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R249" s="1" t="s">
         <v>30</v>
@@ -20068,13 +20068,13 @@
         <v>27</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H251" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I251" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J251" s="1" t="s">
         <v>1497</v>
@@ -20222,7 +20222,7 @@
         <v>1520</v>
       </c>
       <c r="Q253" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R253" s="1" t="s">
         <v>30</v>
@@ -20271,7 +20271,7 @@
         <v>293</v>
       </c>
       <c r="L254" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M254" s="1" t="s">
         <v>1524</v>
@@ -20284,7 +20284,7 @@
       </c>
       <c r="P254" s="1"/>
       <c r="Q254" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R254" s="1" t="s">
         <v>30</v>
@@ -20333,7 +20333,7 @@
         <v>293</v>
       </c>
       <c r="L255" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M255" s="1" t="s">
         <v>1524</v>
@@ -20346,7 +20346,7 @@
       </c>
       <c r="P255" s="1"/>
       <c r="Q255" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R255" s="1" t="s">
         <v>30</v>
@@ -20466,7 +20466,7 @@
       </c>
       <c r="P257" s="1"/>
       <c r="Q257" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R257" s="1" t="s">
         <v>30</v>
@@ -20875,7 +20875,7 @@
         <v>1590</v>
       </c>
       <c r="L264" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M264" s="1" t="s">
         <v>1591</v>
@@ -20888,7 +20888,7 @@
       </c>
       <c r="P264" s="1"/>
       <c r="Q264" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R264" s="1" t="s">
         <v>30</v>
@@ -20939,7 +20939,7 @@
         <v>1590</v>
       </c>
       <c r="L265" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M265" s="1" t="s">
         <v>1596</v>
@@ -20952,7 +20952,7 @@
       </c>
       <c r="P265" s="1"/>
       <c r="Q265" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R265" s="1" t="s">
         <v>30</v>
@@ -20999,7 +20999,7 @@
         <v>572</v>
       </c>
       <c r="L266" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M266" s="1" t="s">
         <v>1605</v>
@@ -21012,7 +21012,7 @@
       </c>
       <c r="P266" s="1"/>
       <c r="Q266" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R266" s="1" t="s">
         <v>30</v>
@@ -21112,13 +21112,13 @@
         <v>27</v>
       </c>
       <c r="G268" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H268" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I268" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J268" s="1" t="s">
         <v>1618</v>
@@ -21140,7 +21140,7 @@
       </c>
       <c r="P268" s="1"/>
       <c r="Q268" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R268" s="1" t="s">
         <v>30</v>
@@ -21187,7 +21187,7 @@
         <v>293</v>
       </c>
       <c r="L269" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M269" s="1" t="s">
         <v>1626</v>
@@ -21251,7 +21251,7 @@
         <v>1635</v>
       </c>
       <c r="L270" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="M270" s="1" t="s">
         <v>1636</v>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="P270" s="1"/>
       <c r="Q270" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R270" s="1" t="s">
         <v>30</v>
@@ -21324,7 +21324,7 @@
       </c>
       <c r="P271" s="1"/>
       <c r="Q271" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R271" s="1" t="s">
         <v>30</v>
@@ -21373,7 +21373,7 @@
         <v>768</v>
       </c>
       <c r="L272" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M272" s="1" t="s">
         <v>1648</v>
@@ -21435,7 +21435,7 @@
         <v>768</v>
       </c>
       <c r="L273" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M273" s="1" t="s">
         <v>1648</v>
@@ -21501,7 +21501,7 @@
         <v>59</v>
       </c>
       <c r="L274" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M274" s="1" t="s">
         <v>1660</v>
@@ -21565,7 +21565,7 @@
         <v>59</v>
       </c>
       <c r="L275" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M275" s="1" t="s">
         <v>1669</v>
@@ -21614,13 +21614,13 @@
         <v>209</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H276" s="1" t="s">
         <v>1676</v>
       </c>
       <c r="I276" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J276" s="1" t="s">
         <v>1677</v>
@@ -21644,7 +21644,7 @@
         <v>1680</v>
       </c>
       <c r="Q276" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R276" s="1" t="s">
         <v>30</v>
@@ -21680,13 +21680,13 @@
         <v>209</v>
       </c>
       <c r="G277" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H277" s="1" t="s">
         <v>1676</v>
       </c>
       <c r="I277" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J277" s="1" t="s">
         <v>1677</v>
@@ -21710,7 +21710,7 @@
         <v>1680</v>
       </c>
       <c r="Q277" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R277" s="1" t="s">
         <v>30</v>
@@ -21772,7 +21772,7 @@
       </c>
       <c r="P278" s="1"/>
       <c r="Q278" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R278" s="1" t="s">
         <v>30</v>
@@ -21836,7 +21836,7 @@
       </c>
       <c r="P279" s="1"/>
       <c r="Q279" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R279" s="1" t="s">
         <v>30</v>
@@ -21900,7 +21900,7 @@
       </c>
       <c r="P280" s="1"/>
       <c r="Q280" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R280" s="1" t="s">
         <v>30</v>
@@ -21960,7 +21960,7 @@
       </c>
       <c r="P281" s="1"/>
       <c r="Q281" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R281" s="1" t="s">
         <v>30</v>
@@ -22080,7 +22080,7 @@
       </c>
       <c r="P283" s="1"/>
       <c r="Q283" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R283" s="1" t="s">
         <v>30</v>
@@ -22142,7 +22142,7 @@
       </c>
       <c r="P284" s="1"/>
       <c r="Q284" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R284" s="1" t="s">
         <v>30</v>
@@ -22382,7 +22382,7 @@
         <v>1762</v>
       </c>
       <c r="Q288" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R288" s="1" t="s">
         <v>30</v>
@@ -22444,7 +22444,7 @@
       </c>
       <c r="P289" s="1"/>
       <c r="Q289" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R289" s="1" t="s">
         <v>30</v>
@@ -22479,7 +22479,7 @@
         <v>30</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G290" s="1" t="s">
         <v>1776</v>
@@ -22493,20 +22493,20 @@
         <v>1778</v>
       </c>
       <c r="L290" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M290" s="1" t="s">
         <v>1775</v>
       </c>
       <c r="N290" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O290" s="1" t="s">
         <v>1779</v>
       </c>
       <c r="P290" s="1"/>
       <c r="Q290" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R290" s="1" t="s">
         <v>30</v>
@@ -22539,7 +22539,7 @@
         <v>30</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G291" s="1"/>
       <c r="H291" s="1"/>
@@ -22551,20 +22551,20 @@
         <v>1783</v>
       </c>
       <c r="L291" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M291" s="1" t="s">
         <v>1775</v>
       </c>
       <c r="N291" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O291" s="1" t="s">
         <v>1784</v>
       </c>
       <c r="P291" s="1"/>
       <c r="Q291" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R291" s="1" t="s">
         <v>30</v>
